--- a/羅老師藥劑試驗.xlsx
+++ b/羅老師藥劑試驗.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nmbdcrc\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\藥效測試\practice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{24F0D75B-C625-40EA-B57E-D0DB19F0445F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C38F556-C02E-428C-9AEC-0D4F448D174B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{654F54CC-900E-42FC-B005-0FFE29B6F0D8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{654F54CC-900E-42FC-B005-0FFE29B6F0D8}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="45">
   <si>
     <t>年</t>
   </si>
@@ -183,7 +183,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="179" formatCode="m/d"/>
+    <numFmt numFmtId="176" formatCode="m/d"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -224,14 +224,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -548,7 +545,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EECDBDC-25F7-4B49-AB10-39893CAF86C2}">
-  <dimension ref="A1:E62"/>
+  <dimension ref="A1:E63"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="9.5" style="1" bestFit="1" customWidth="1"/>
@@ -767,10 +764,10 @@
         <v>46107</v>
       </c>
       <c r="C13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D13">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="E13" t="s">
         <v>7</v>
@@ -787,7 +784,7 @@
         <v>13</v>
       </c>
       <c r="D14">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E14" t="s">
         <v>7</v>
@@ -801,10 +798,10 @@
         <v>46107</v>
       </c>
       <c r="C15" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E15" t="s">
         <v>7</v>
@@ -821,7 +818,7 @@
         <v>14</v>
       </c>
       <c r="D16">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E16" t="s">
         <v>7</v>
@@ -835,10 +832,10 @@
         <v>46107</v>
       </c>
       <c r="C17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D17">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E17" t="s">
         <v>7</v>
@@ -855,7 +852,7 @@
         <v>15</v>
       </c>
       <c r="D18">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E18" t="s">
         <v>7</v>
@@ -866,13 +863,13 @@
         <v>2025</v>
       </c>
       <c r="B19" s="1">
-        <v>46108</v>
+        <v>46107</v>
       </c>
       <c r="C19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D19">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E19" t="s">
         <v>7</v>
@@ -889,7 +886,7 @@
         <v>16</v>
       </c>
       <c r="D20">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E20" t="s">
         <v>7</v>
@@ -903,10 +900,10 @@
         <v>46108</v>
       </c>
       <c r="C21" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D21">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E21" t="s">
         <v>7</v>
@@ -923,7 +920,7 @@
         <v>17</v>
       </c>
       <c r="D22">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E22" t="s">
         <v>7</v>
@@ -937,10 +934,10 @@
         <v>46108</v>
       </c>
       <c r="C23" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D23">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E23" t="s">
         <v>7</v>
@@ -957,7 +954,7 @@
         <v>18</v>
       </c>
       <c r="D24">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E24" t="s">
         <v>7</v>
@@ -971,10 +968,10 @@
         <v>46108</v>
       </c>
       <c r="C25" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D25">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E25" t="s">
         <v>7</v>
@@ -991,7 +988,7 @@
         <v>19</v>
       </c>
       <c r="D26">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E26" t="s">
         <v>7</v>
@@ -1002,16 +999,16 @@
         <v>2025</v>
       </c>
       <c r="B27" s="1">
-        <v>46196</v>
+        <v>46108</v>
       </c>
       <c r="C27" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D27">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="E27" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -1025,7 +1022,7 @@
         <v>20</v>
       </c>
       <c r="D28">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="E28" t="s">
         <v>22</v>
@@ -1039,10 +1036,10 @@
         <v>46196</v>
       </c>
       <c r="C29" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D29">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="E29" t="s">
         <v>22</v>
@@ -1059,7 +1056,7 @@
         <v>21</v>
       </c>
       <c r="D30">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="E30" t="s">
         <v>22</v>
@@ -1070,16 +1067,16 @@
         <v>2025</v>
       </c>
       <c r="B31" s="1">
-        <v>46261</v>
+        <v>46196</v>
       </c>
       <c r="C31" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D31">
         <v>32</v>
       </c>
       <c r="E31" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -1093,7 +1090,7 @@
         <v>23</v>
       </c>
       <c r="D32">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="E32" t="s">
         <v>24</v>
@@ -1104,16 +1101,16 @@
         <v>2025</v>
       </c>
       <c r="B33" s="1">
-        <v>46310</v>
+        <v>46261</v>
       </c>
       <c r="C33" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D33">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="E33" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -1127,7 +1124,7 @@
         <v>25</v>
       </c>
       <c r="D34">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="E34" t="s">
         <v>26</v>
@@ -1141,13 +1138,13 @@
         <v>46310</v>
       </c>
       <c r="C35" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D35">
-        <v>128</v>
+        <v>100</v>
       </c>
       <c r="E35" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -1155,16 +1152,16 @@
         <v>2025</v>
       </c>
       <c r="B36" s="1">
-        <v>45952</v>
+        <v>46310</v>
       </c>
       <c r="C36" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D36">
-        <v>25</v>
+        <v>128</v>
       </c>
       <c r="E36" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -1172,16 +1169,16 @@
         <v>2025</v>
       </c>
       <c r="B37" s="1">
-        <v>46379</v>
+        <v>45952</v>
       </c>
       <c r="C37" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D37">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E37" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -1195,7 +1192,7 @@
         <v>29</v>
       </c>
       <c r="D38">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="E38" t="s">
         <v>33</v>
@@ -1209,10 +1206,10 @@
         <v>46379</v>
       </c>
       <c r="C39" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D39">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="E39" t="s">
         <v>33</v>
@@ -1229,7 +1226,7 @@
         <v>30</v>
       </c>
       <c r="D40">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="E40" t="s">
         <v>33</v>
@@ -1243,10 +1240,10 @@
         <v>46379</v>
       </c>
       <c r="C41" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D41">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="E41" t="s">
         <v>33</v>
@@ -1263,7 +1260,7 @@
         <v>31</v>
       </c>
       <c r="D42">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="E42" t="s">
         <v>33</v>
@@ -1277,10 +1274,10 @@
         <v>46379</v>
       </c>
       <c r="C43" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D43">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="E43" t="s">
         <v>33</v>
@@ -1297,7 +1294,7 @@
         <v>32</v>
       </c>
       <c r="D44">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="E44" t="s">
         <v>33</v>
@@ -1305,19 +1302,19 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="B45" s="1">
-        <v>46035</v>
+        <v>46379</v>
       </c>
       <c r="C45" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D45">
-        <v>30</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>40</v>
+        <v>100</v>
+      </c>
+      <c r="E45" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
@@ -1331,9 +1328,9 @@
         <v>34</v>
       </c>
       <c r="D46">
-        <v>100</v>
-      </c>
-      <c r="E46" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E46" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1345,12 +1342,12 @@
         <v>46035</v>
       </c>
       <c r="C47" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D47">
-        <v>30</v>
-      </c>
-      <c r="E47" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E47" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1365,9 +1362,9 @@
         <v>35</v>
       </c>
       <c r="D48">
-        <v>100</v>
-      </c>
-      <c r="E48" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E48" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1379,12 +1376,12 @@
         <v>46035</v>
       </c>
       <c r="C49" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D49">
-        <v>30</v>
-      </c>
-      <c r="E49" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E49" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1399,9 +1396,9 @@
         <v>36</v>
       </c>
       <c r="D50">
-        <v>100</v>
-      </c>
-      <c r="E50" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E50" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1413,12 +1410,12 @@
         <v>46035</v>
       </c>
       <c r="C51" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D51">
-        <v>30</v>
-      </c>
-      <c r="E51" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E51" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1433,9 +1430,9 @@
         <v>37</v>
       </c>
       <c r="D52">
-        <v>100</v>
-      </c>
-      <c r="E52" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E52" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1444,15 +1441,15 @@
         <v>2026</v>
       </c>
       <c r="B53" s="1">
-        <v>46036</v>
+        <v>46035</v>
       </c>
       <c r="C53" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D53">
-        <v>30</v>
-      </c>
-      <c r="E53" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E53" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1467,9 +1464,9 @@
         <v>38</v>
       </c>
       <c r="D54">
-        <v>100</v>
-      </c>
-      <c r="E54" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E54" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1481,12 +1478,12 @@
         <v>46036</v>
       </c>
       <c r="C55" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D55">
-        <v>30</v>
-      </c>
-      <c r="E55" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E55" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1501,9 +1498,9 @@
         <v>39</v>
       </c>
       <c r="D56">
-        <v>100</v>
-      </c>
-      <c r="E56" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E56" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1512,16 +1509,16 @@
         <v>2026</v>
       </c>
       <c r="B57" s="1">
-        <v>46125</v>
+        <v>46036</v>
       </c>
       <c r="C57" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D57">
-        <v>50</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>42</v>
+        <v>100</v>
+      </c>
+      <c r="E57" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
@@ -1535,9 +1532,9 @@
         <v>41</v>
       </c>
       <c r="D58">
-        <v>100</v>
-      </c>
-      <c r="E58" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E58" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1549,13 +1546,13 @@
         <v>46125</v>
       </c>
       <c r="C59" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="D59">
         <v>100</v>
       </c>
-      <c r="E59" s="2" t="s">
-        <v>44</v>
+      <c r="E59" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
@@ -1569,9 +1566,9 @@
         <v>8</v>
       </c>
       <c r="D60">
-        <v>200</v>
-      </c>
-      <c r="E60" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E60" t="s">
         <v>44</v>
       </c>
     </row>
@@ -1580,16 +1577,16 @@
         <v>2026</v>
       </c>
       <c r="B61" s="1">
-        <v>46133</v>
+        <v>46125</v>
       </c>
       <c r="C61" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="D61">
         <v>200</v>
       </c>
-      <c r="E61" s="2" t="s">
-        <v>43</v>
+      <c r="E61" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
@@ -1600,12 +1597,29 @@
         <v>46133</v>
       </c>
       <c r="C62" t="s">
+        <v>41</v>
+      </c>
+      <c r="D62">
+        <v>200</v>
+      </c>
+      <c r="E62" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>2026</v>
+      </c>
+      <c r="B63" s="1">
+        <v>46133</v>
+      </c>
+      <c r="C63" t="s">
         <v>8</v>
       </c>
-      <c r="D62">
+      <c r="D63">
         <v>400</v>
       </c>
-      <c r="E62" s="2" t="s">
+      <c r="E63" t="s">
         <v>43</v>
       </c>
     </row>
